--- a/avito-feed/shacman_sx331863366.xlsx
+++ b/avito-feed/shacman_sx331863366.xlsx
@@ -804,13 +804,6 @@
           <t>shacman-sx331863366-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -835,15 +828,11 @@
       <c r="L2" t="n">
         <v>4500000</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 5</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>Shacman</t>
@@ -877,8 +866,6 @@
           <t>Механика</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>Грузовики</t>
@@ -894,22 +881,11 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
           <t>С пробегом</t>
@@ -923,21 +899,14 @@
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
         <v>35</v>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr">
         <is>
           <t>LZGJX4Z61PX013400</t>
@@ -946,9 +915,6 @@
       <c r="BG2" t="n">
         <v>2023</v>
       </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr">
         <is>
           <t>Евро 5</t>
